--- a/Datalist/PVZ3DWavesInfo.xlsx
+++ b/Datalist/PVZ3DWavesInfo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnrealProject\PVZ3D\Datalist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{FDDAD0FE-1EF8-4986-B6FB-D7D0BA4EB245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5286C8A0-E3B4-4EA2-B763-EF23270F5670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25320" yWindow="450" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="23">
   <si>
     <t>1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -107,11 +107,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SpawnInterval</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TimeLimit</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -469,7 +473,10 @@
         <v>9</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -493,7 +500,10 @@
         <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>10</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -519,6 +529,9 @@
       <c r="F3" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="G3">
+        <v>10</v>
+      </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
@@ -541,7 +554,10 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>10</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -565,7 +581,10 @@
         <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="G5">
+        <v>10</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -591,6 +610,9 @@
       <c r="F6" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="G6">
+        <v>10</v>
+      </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -615,6 +637,9 @@
       <c r="F7" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="G7">
+        <v>10</v>
+      </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -639,6 +664,9 @@
       <c r="F8" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -662,6 +690,9 @@
       </c>
       <c r="F9" s="1" t="s">
         <v>11</v>
+      </c>
+      <c r="G9">
+        <v>10</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
